--- a/results/02_taxa_assemblage/WardsClustering/tables/pvclust_AU_sweep_3_(40, 70).xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/pvclust_AU_sweep_3_(40, 70).xlsx
@@ -496,31 +496,31 @@
         <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5562</v>
+        <v>0.8799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0034</v>
+        <v>0.0487</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9522</v>
+        <v>0.904</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0139</v>
+        <v>0.4999</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9606</v>
+        <v>0.8772</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8206</v>
+        <v>0.034</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -534,31 +534,31 @@
         <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4864</v>
+        <v>0.7867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0035</v>
+        <v>0.0181</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6149</v>
+        <v>0.9042</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1502</v>
+        <v>0.4995</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6462</v>
+        <v>0.5279</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0188</v>
+        <v>0.0034</v>
       </c>
       <c r="L3" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -572,31 +572,31 @@
         <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6189</v>
+        <v>0.8552</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0188</v>
+        <v>0.019</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4623</v>
+        <v>0.9052</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0035</v>
+        <v>0.4997</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6331</v>
+        <v>0.5502</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1479</v>
+        <v>0.0034</v>
       </c>
       <c r="L4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -610,31 +610,31 @@
         <v>43</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6616</v>
+        <v>0.7733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0198</v>
+        <v>0.0163</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.018</v>
+        <v>0.906</v>
       </c>
       <c r="H5" t="n">
-        <v>0.018</v>
+        <v>0.5008</v>
       </c>
       <c r="I5" t="n">
         <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5709</v>
+        <v>0.08</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1045</v>
+        <v>0.08</v>
       </c>
       <c r="L5" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -648,31 +648,31 @@
         <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3752</v>
+        <v>0.8066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0065</v>
+        <v>0.0263</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.9062</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5703</v>
+        <v>0.9364</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1108</v>
+        <v>0.0345</v>
       </c>
       <c r="L6" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -686,31 +686,31 @@
         <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.7873</v>
       </c>
       <c r="E7" t="n">
-        <v>0.014</v>
+        <v>0.0203</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008</v>
+        <v>0.8994</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008</v>
+        <v>0.4972</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5769</v>
+        <v>0.7313</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1107</v>
+        <v>0.0078</v>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -724,31 +724,31 @@
         <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5961</v>
+        <v>0.802</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0197</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>0.014</v>
+        <v>0.9013</v>
       </c>
       <c r="H8" t="n">
-        <v>0.014</v>
+        <v>0.4965</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5615</v>
+        <v>0.5837</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0397</v>
+        <v>0.0067</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -762,31 +762,31 @@
         <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5669</v>
+        <v>0.7887</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0322</v>
+        <v>0.0182</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7417</v>
+        <v>0.9013</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0139</v>
+        <v>0.4958</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.7875</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8097</v>
+        <v>0.0063</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -800,28 +800,28 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5581</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0431</v>
+        <v>0.0145</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5704</v>
+        <v>0.9101</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.4977</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9563</v>
+        <v>0.7261</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2371</v>
+        <v>0.0061</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -838,28 +838,28 @@
         <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5525</v>
+        <v>0.423</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0428</v>
+        <v>0.0138</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6385</v>
+        <v>0.9101</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0089</v>
+        <v>0.497</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.641</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2328</v>
+        <v>0.0069</v>
       </c>
       <c r="L11" t="n">
         <v>3</v>
@@ -876,28 +876,28 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5893</v>
+        <v>0.6682</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0421</v>
+        <v>0.0157</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6522</v>
+        <v>0.9149</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0092</v>
+        <v>0.4974</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9553</v>
+        <v>0.641</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2343</v>
+        <v>0.0069</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -914,31 +914,31 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.6041</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0181</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>0.056</v>
+        <v>0.9127</v>
       </c>
       <c r="H13" t="n">
-        <v>0.056</v>
+        <v>0.4974</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6198</v>
+        <v>0.421</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0317</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -952,31 +952,31 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4697</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0178</v>
       </c>
       <c r="F14" t="n">
         <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>0.058</v>
+        <v>0.8717</v>
       </c>
       <c r="H14" t="n">
-        <v>0.058</v>
+        <v>0.4417</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.1668</v>
       </c>
       <c r="K14" t="n">
-        <v>0.031</v>
+        <v>0.0083</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -990,31 +990,31 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>0.076</v>
+        <v>0.6737</v>
       </c>
       <c r="E15" t="n">
-        <v>0.076</v>
+        <v>0.0166</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.046</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.046</v>
+        <v>0.4407</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.283</v>
       </c>
       <c r="K15" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0078</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1028,31 +1028,31 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>0.062</v>
+        <v>0.6926</v>
       </c>
       <c r="E16" t="n">
-        <v>0.062</v>
+        <v>0.0174</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>0.046</v>
+        <v>0.8689</v>
       </c>
       <c r="H16" t="n">
-        <v>0.046</v>
+        <v>0.4435</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0071</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1066,31 +1066,31 @@
         <v>55</v>
       </c>
       <c r="D17" t="n">
-        <v>0.054</v>
+        <v>0.6498</v>
       </c>
       <c r="E17" t="n">
-        <v>0.054</v>
+        <v>0.0171</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5841</v>
+        <v>0.8656</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0117</v>
+        <v>0.4431</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>0.672</v>
+        <v>0.2632</v>
       </c>
       <c r="K17" t="n">
-        <v>0.006</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1104,31 +1104,31 @@
         <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04</v>
+        <v>0.6126</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04</v>
+        <v>0.0153</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>0.599</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0116</v>
+        <v>0.4432</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7343</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0058</v>
+        <v>0.0081</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1142,31 +1142,31 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>0.066</v>
+        <v>0.673</v>
       </c>
       <c r="E19" t="n">
-        <v>0.066</v>
+        <v>0.0175</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9153</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0394</v>
+        <v>0.445</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5244</v>
+        <v>0.2225</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0045</v>
+        <v>0.0092</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1180,31 +1180,31 @@
         <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1289</v>
+        <v>0.5769</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0039</v>
+        <v>0.0131</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9101</v>
+        <v>0.7914</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0409</v>
+        <v>0.1617</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6218</v>
+        <v>0.2568</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0054</v>
+        <v>0.0089</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1218,31 +1218,31 @@
         <v>59</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7663</v>
+        <v>0.5567</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0044</v>
+        <v>0.0151</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9208</v>
+        <v>0.7872</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0418</v>
+        <v>0.1616</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7972</v>
+        <v>0.4709</v>
       </c>
       <c r="K21" t="n">
-        <v>0.007</v>
+        <v>0.0091</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1256,31 +1256,31 @@
         <v>60</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4868</v>
+        <v>0.8403</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0035</v>
+        <v>0.0345</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9193</v>
+        <v>0.6866</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0418</v>
+        <v>0.0477</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7972</v>
+        <v>0.64</v>
       </c>
       <c r="K22" t="n">
-        <v>0.007</v>
+        <v>0.0061</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1294,31 +1294,31 @@
         <v>61</v>
       </c>
       <c r="D23" t="n">
-        <v>0.054</v>
+        <v>0.907</v>
       </c>
       <c r="E23" t="n">
-        <v>0.054</v>
+        <v>0.0361</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5935</v>
+        <v>0.6657</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0048</v>
+        <v>0.0472</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9485</v>
+        <v>0.878</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0505</v>
+        <v>0.0039</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1332,31 +1332,31 @@
         <v>62</v>
       </c>
       <c r="D24" t="n">
-        <v>0.052</v>
+        <v>0.6708</v>
       </c>
       <c r="E24" t="n">
-        <v>0.052</v>
+        <v>0.0199</v>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6871</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0052</v>
+        <v>0.0472</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9425</v>
+        <v>0.1355</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0503</v>
+        <v>0.0071</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1370,31 +1370,31 @@
         <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4899</v>
+        <v>0.7714</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0035</v>
+        <v>0.0208</v>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4855</v>
+        <v>0.8014</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0068</v>
+        <v>0.0353</v>
       </c>
       <c r="I25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9455</v>
+        <v>0.824</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0509</v>
+        <v>0.0034</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1408,31 +1408,31 @@
         <v>64</v>
       </c>
       <c r="D26" t="n">
-        <v>0.481</v>
+        <v>0.8008</v>
       </c>
       <c r="E26" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F26" t="n">
+        <v>41</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K26" t="n">
         <v>0.0034</v>
       </c>
-      <c r="F26" t="n">
-        <v>48</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.7981</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.9643</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.0532</v>
-      </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1446,31 +1446,31 @@
         <v>65</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5258</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0034</v>
+        <v>0.0236</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7694</v>
+        <v>0.7911</v>
       </c>
       <c r="H27" t="n">
-        <v>0.008</v>
+        <v>0.0364</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9606</v>
+        <v>0.8991</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0529</v>
+        <v>0.0051</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1484,31 +1484,31 @@
         <v>66</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5228</v>
+        <v>0.8721</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0034</v>
+        <v>0.0252</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7511</v>
+        <v>0.7816</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0067</v>
+        <v>0.0356</v>
       </c>
       <c r="I28" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9641</v>
+        <v>0.4808</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0522</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1522,31 +1522,31 @@
         <v>67</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5228</v>
+        <v>0.9283</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0034</v>
+        <v>0.0225</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8437</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0044</v>
+        <v>0.035</v>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9308</v>
+        <v>0.0114</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0503</v>
+        <v>0.0146</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1560,31 +1560,31 @@
         <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03</v>
+        <v>0.9267</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03</v>
+        <v>0.0209</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8985</v>
+        <v>0.8182</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0057</v>
+        <v>0.0341</v>
       </c>
       <c r="I30" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7887</v>
+        <v>0.0114</v>
       </c>
       <c r="K30" t="n">
-        <v>0.012</v>
+        <v>0.0146</v>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1598,31 +1598,31 @@
         <v>69</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9246</v>
+        <v>0.8046</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0063</v>
+        <v>0.0341</v>
       </c>
       <c r="I31" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7256</v>
+        <v>0.5903</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0114</v>
+        <v>0.0065</v>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1636,31 +1636,31 @@
         <v>70</v>
       </c>
       <c r="D32" t="n">
-        <v>0.026</v>
+        <v>0.6359</v>
       </c>
       <c r="E32" t="n">
-        <v>0.026</v>
+        <v>0.0213</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G32" t="n">
-        <v>0.874</v>
+        <v>0.9911</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0035</v>
+        <v>0.646</v>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8184</v>
+        <v>0.5654</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0115</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
